--- a/sbs_historical_data.xlsx
+++ b/sbs_historical_data.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2137"/>
+  <dimension ref="A1:F2145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -51839,6 +51839,198 @@
       </c>
       <c r="F2137" s="5" t="n">
         <v>61.8172524</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="3" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2138" s="4" t="inlineStr">
+        <is>
+          <t>AFP Habitat</t>
+        </is>
+      </c>
+      <c r="C2138" s="5" t="n">
+        <v>16.05152</v>
+      </c>
+      <c r="D2138" s="5" t="n">
+        <v>23.9320318</v>
+      </c>
+      <c r="E2138" s="5" t="n">
+        <v>27.595587</v>
+      </c>
+      <c r="F2138" s="5" t="n">
+        <v>31.0525179</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="3" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2139" s="4" t="inlineStr">
+        <is>
+          <t>AFP Integra</t>
+        </is>
+      </c>
+      <c r="C2139" s="5" t="n">
+        <v>15.4970555</v>
+      </c>
+      <c r="D2139" s="5" t="n">
+        <v>34.9179138</v>
+      </c>
+      <c r="E2139" s="5" t="n">
+        <v>294.8684618</v>
+      </c>
+      <c r="F2139" s="5" t="n">
+        <v>68.39641210000001</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="3" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2140" s="4" t="inlineStr">
+        <is>
+          <t>AFP Profuturo</t>
+        </is>
+      </c>
+      <c r="C2140" s="5" t="n">
+        <v>15.6691478</v>
+      </c>
+      <c r="D2140" s="5" t="n">
+        <v>33.2013878</v>
+      </c>
+      <c r="E2140" s="5" t="n">
+        <v>266.4209954</v>
+      </c>
+      <c r="F2140" s="5" t="n">
+        <v>68.1915456</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="3" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2141" s="4" t="inlineStr">
+        <is>
+          <t>Prima AFP</t>
+        </is>
+      </c>
+      <c r="C2141" s="5" t="n">
+        <v>15.6644407</v>
+      </c>
+      <c r="D2141" s="5" t="n">
+        <v>38.7091969</v>
+      </c>
+      <c r="E2141" s="5" t="n">
+        <v>55.4059756</v>
+      </c>
+      <c r="F2141" s="5" t="n">
+        <v>61.5390748</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B2142" s="4" t="inlineStr">
+        <is>
+          <t>AFP Habitat</t>
+        </is>
+      </c>
+      <c r="C2142" s="5" t="n">
+        <v>16.0462</v>
+      </c>
+      <c r="D2142" s="5" t="n">
+        <v>23.9128862</v>
+      </c>
+      <c r="E2142" s="5" t="n">
+        <v>27.5459149</v>
+      </c>
+      <c r="F2142" s="5" t="n">
+        <v>30.9748866</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B2143" s="4" t="inlineStr">
+        <is>
+          <t>AFP Integra</t>
+        </is>
+      </c>
+      <c r="C2143" s="5" t="n">
+        <v>15.4919193</v>
+      </c>
+      <c r="D2143" s="5" t="n">
+        <v>34.8899795</v>
+      </c>
+      <c r="E2143" s="5" t="n">
+        <v>294.3376981</v>
+      </c>
+      <c r="F2143" s="5" t="n">
+        <v>68.22542110000001</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B2144" s="4" t="inlineStr">
+        <is>
+          <t>AFP Profuturo</t>
+        </is>
+      </c>
+      <c r="C2144" s="5" t="n">
+        <v>15.6639546</v>
+      </c>
+      <c r="D2144" s="5" t="n">
+        <v>33.1748268</v>
+      </c>
+      <c r="E2144" s="5" t="n">
+        <v>265.9414372</v>
+      </c>
+      <c r="F2144" s="5" t="n">
+        <v>68.0210668</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B2145" s="4" t="inlineStr">
+        <is>
+          <t>Prima AFP</t>
+        </is>
+      </c>
+      <c r="C2145" s="5" t="n">
+        <v>15.659249</v>
+      </c>
+      <c r="D2145" s="5" t="n">
+        <v>38.6782296</v>
+      </c>
+      <c r="E2145" s="5" t="n">
+        <v>55.3062448</v>
+      </c>
+      <c r="F2145" s="5" t="n">
+        <v>61.3852271</v>
       </c>
     </row>
   </sheetData>
@@ -51866,7 +52058,7 @@
       <c r="A1" s="6" t="inlineStr">
         <is>
           <t>REPORTE SBS FP-1359: VALORES CUOTA DIARIOS VIGENTES
-Cierre Estadístico Oficial al 18/05/2026</t>
+Cierre Estadístico Oficial al 20/05/2026</t>
         </is>
       </c>
     </row>
@@ -51905,16 +52097,16 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>16.0569709</v>
+        <v>16.0462</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>23.9607847</v>
+        <v>23.9128862</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>27.6730716</v>
+        <v>27.5459149</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>31.1928859</v>
+        <v>30.9748866</v>
       </c>
     </row>
     <row r="6">
@@ -51924,16 +52116,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>15.4999932</v>
+        <v>15.4919193</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>34.9598656</v>
+        <v>34.8899795</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>295.6964117</v>
+        <v>294.3376981</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>68.7055873</v>
+        <v>68.22542110000001</v>
       </c>
     </row>
     <row r="7">
@@ -51943,16 +52135,16 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>15.6721181</v>
+        <v>15.6639546</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>33.2412773</v>
+        <v>33.1748268</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>267.1690688</v>
+        <v>265.9414372</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>68.4997947</v>
+        <v>68.0210668</v>
       </c>
     </row>
     <row r="8">
@@ -51962,16 +52154,16 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>15.6674101</v>
+        <v>15.659249</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>38.7557037</v>
+        <v>38.6782296</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>55.561548</v>
+        <v>55.3062448</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>61.8172524</v>
+        <v>61.3852271</v>
       </c>
     </row>
   </sheetData>
